--- a/quizzes/010_programming_variables_quiz--quizzes.xlsx
+++ b/quizzes/010_programming_variables_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Seventh Page</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Eighth Page</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Ninth Page</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Tenth Page</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Eleventh Page</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twelfth Page</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Thirteenth Page</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Fourteenth Page</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Fifteenth Page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Sixteenth Page</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Seventeenth Page</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Eighteenth Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Nineteenth Page</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Tentieth Page</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentyfirst Page</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentysecond Page</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentythird Page</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentyfourth Page</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentyfifth Page</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentysixth Page</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentysseventh Page</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentyeighth Page</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Twentyninth Page</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>What is the correct data type for the following?</t>
+          <t>Programming Variables Quiz Thirtieth Page</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1325,8 +1325,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'integer'}</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Integer'}</t>
+          <t>Integer</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'boolean'}</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Boolean'}</t>
+          <t>Boolean</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'array'}</t>
+          <t>array</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Array'}</t>
+          <t>Array</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'global'}</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Global'}</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2425,12 +2425,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3139,12 +3139,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3173,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3360,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3428,12 +3428,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3530,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'int'}</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Int'}</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'float'}</t>
+          <t>float</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Float'}</t>
+          <t>Float</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'char'}</t>
+          <t>char</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Char'}</t>
+          <t>Char</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'string'}</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'String'}</t>
+          <t>String</t>
         </is>
       </c>
     </row>
@@ -3598,12 +3598,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
